--- a/ODS - Foundations & Process Planner.xlsx
+++ b/ODS - Foundations & Process Planner.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patsandh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krianoop1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C83031C-8401-40AE-851F-60D237540C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6301CC21-9BA8-4CC4-BDEB-6FB65FCC6A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{188CA9A8-EC5F-4E0E-81F4-63EA615ED8B3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{188CA9A8-EC5F-4E0E-81F4-63EA615ED8B3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Updated-3day plan" sheetId="2" r:id="rId1"/>
-    <sheet name="5 Day planner" sheetId="3" r:id="rId2"/>
+    <sheet name="Foundation Training - ODS - 3D" sheetId="2" r:id="rId1"/>
+    <sheet name="Process Training - ODS - 5D" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -284,9 +284,6 @@
     <t>Quick Wrap-up</t>
   </si>
   <si>
-    <t>LLM/system prediction; independent human decision; comparison; identifying whether system/customer decision is correct;</t>
-  </si>
-  <si>
     <t>Recap - Day 1</t>
   </si>
   <si>
@@ -345,12 +342,6 @@
 Common lures: delivery, bank, prize, account locked, etc</t>
   </si>
   <si>
-    <t xml:space="preserve">How Sentinel Works? 
-Rheoritcal Method - via Splunk dashboard
-How to retrieve and assign cases from queues?
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">End-to-end journey
 High-level queue flow
 What is Signature ID, Sender, Count, etc
@@ -376,11 +367,6 @@
     <t>Purpose of dashboard; 
 what trainees will review; 
 Relationship to case queues;</t>
-  </si>
-  <si>
-    <t>Why the message was moved/reported as Not Junk; 
-How to review a case in Sentinel?
-Tool Selection &amp; Investigation Flow</t>
   </si>
   <si>
     <t>Trainees work on a group of 2 or 4, and action the same cases, and the trainers discuss each cases on the screen and clarify any challenges.</t>
@@ -422,9 +408,6 @@
     <t>Recap - Day 4</t>
   </si>
   <si>
-    <t>All the practice and assessment would be conducted on Google forms/Numbers/Other tools and No action would be processed on the actual tools</t>
-  </si>
-  <si>
     <t>Final Assessment</t>
   </si>
   <si>
@@ -475,6 +458,26 @@
   </si>
   <si>
     <t xml:space="preserve">Mixed cases across all three queues; final label/decision; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">How Sentinel Works? 
+How to retrieve and assign cases from queues?
+</t>
+  </si>
+  <si>
+    <t>Why the message was moved/reported as Not Junk; 
+Rheoritcal Method - via Splunk dashboard
+Signature ID and Sender ID cases
+How to review a case in Sentinel?
+Tool Selection &amp; Investigation Flow</t>
+  </si>
+  <si>
+    <t>LLM/system prediction
+ independent human decision
+Identifying whether system/customer decision is correct</t>
+  </si>
+  <si>
+    <t>All the practice and assessment would be conducted on Practice sheet/Numbers and No action would be processed on the actual tools. For Shadowing sessions, trainer would share screen accordingly.</t>
   </si>
 </sst>
 </file>
@@ -754,24 +757,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -796,6 +781,24 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1133,18 +1136,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805439E2-405B-404B-B2CF-A20952B22B34}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" style="2"/>
-    <col min="2" max="2" width="46.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="52.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" style="2"/>
-    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.54296875" style="2"/>
+    <col min="1" max="1" width="9.5546875" style="2"/>
+    <col min="2" max="2" width="46.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="2"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -1161,14 +1164,14 @@
         <v>4</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1184,14 +1187,14 @@
         <v>120</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="29"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="38"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1205,14 +1208,14 @@
         <v>60</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="29"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="38"/>
       <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1224,14 +1227,14 @@
         <v>45</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="87" x14ac:dyDescent="0.35">
-      <c r="A5" s="29"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="38"/>
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
@@ -1245,14 +1248,14 @@
         <v>150</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="29"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
@@ -1266,14 +1269,14 @@
         <v>45</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1289,19 +1292,19 @@
         <v>60</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="29"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="38"/>
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>26</v>
@@ -1310,38 +1313,38 @@
         <v>45</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" s="24">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="29"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="38"/>
       <c r="B9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="7">
         <v>60</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="29"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="38"/>
       <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>30</v>
@@ -1350,19 +1353,19 @@
         <v>50</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="29"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="38"/>
       <c r="B11" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>31</v>
@@ -1371,14 +1374,14 @@
         <v>60</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="29"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="38"/>
       <c r="B12" s="5" t="s">
         <v>32</v>
       </c>
@@ -1392,19 +1395,19 @@
         <v>45</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A13" s="29"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
       <c r="B13" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>35</v>
@@ -1413,14 +1416,14 @@
         <v>90</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="38" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1436,14 +1439,14 @@
         <v>60</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G14" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="29"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="38"/>
       <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
@@ -1457,19 +1460,19 @@
         <v>60</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="29"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
       <c r="B16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>42</v>
@@ -1478,31 +1481,31 @@
         <v>90</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="38"/>
+      <c r="B17" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="9">
         <v>120</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="29"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="38"/>
       <c r="B18" s="9" t="s">
         <v>45</v>
       </c>
@@ -1516,16 +1519,16 @@
         <v>90</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G18" s="12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G19" s="2">
         <f>SUM(G2:G18)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1542,15 +1545,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CE5CC2-4439-454D-9832-9D3ACB1A5FEC}">
   <dimension ref="A1:S34"/>
-  <sheetFormatPr defaultColWidth="17.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="17.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.453125" customWidth="1"/>
-    <col min="3" max="3" width="71.453125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="64.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="8"/>
+    <col min="2" max="2" width="39.44140625" customWidth="1"/>
+    <col min="3" max="3" width="71.44140625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="64.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>1</v>
       </c>
@@ -1567,21 +1570,21 @@
         <v>4</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="28">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="37">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>28</v>
@@ -1590,7 +1593,7 @@
         <v>90</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3">
         <v>2</v>
@@ -1603,34 +1606,34 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="28"/>
+    <row r="3" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="37"/>
       <c r="B3" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>48</v>
       </c>
       <c r="E3" s="13">
         <v>60</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="28"/>
+    <row r="4" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="37"/>
       <c r="B4" s="13" t="s">
         <v>49</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>50</v>
@@ -1639,19 +1642,19 @@
         <v>60</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G4" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="28"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="37"/>
       <c r="B5" s="13" t="s">
         <v>51</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>52</v>
@@ -1660,14 +1663,14 @@
         <v>75</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G5" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="28"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="37"/>
       <c r="B6" s="13" t="s">
         <v>55</v>
       </c>
@@ -1681,19 +1684,19 @@
         <v>45</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G6" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="37"/>
       <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>44</v>
@@ -1702,10 +1705,10 @@
         <v>45</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1720,8 +1723,8 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="28"/>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="37"/>
       <c r="B8" s="13" t="s">
         <v>75</v>
       </c>
@@ -1731,16 +1734,16 @@
         <v>45</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A9" s="28">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="37">
         <v>2</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="15"/>
@@ -1748,17 +1751,17 @@
         <v>45</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="28"/>
+    <row r="10" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="37"/>
       <c r="B10" s="13" t="s">
         <v>53</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>54</v>
@@ -1767,19 +1770,19 @@
         <v>60</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G10" s="15">
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="28"/>
-      <c r="B11" s="33" t="s">
-        <v>119</v>
+    <row r="11" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="37"/>
+      <c r="B11" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>59</v>
@@ -1788,19 +1791,19 @@
         <v>60</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G11" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="28"/>
+    <row r="12" spans="1:19" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="37"/>
       <c r="B12" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>60</v>
@@ -1809,17 +1812,17 @@
         <v>90</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="28"/>
-      <c r="B13" s="34" t="s">
-        <v>123</v>
+    <row r="13" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="37"/>
+      <c r="B13" s="28" t="s">
+        <v>119</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>61</v>
@@ -1828,12 +1831,12 @@
         <v>120</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G13" s="15"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A14" s="28"/>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="37"/>
       <c r="B14" s="13" t="s">
         <v>75</v>
       </c>
@@ -1843,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="15"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A15" s="28">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="37">
         <v>3</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="15"/>
@@ -1860,17 +1863,17 @@
         <v>45</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="28"/>
-      <c r="B16" s="37" t="s">
-        <v>121</v>
+    <row r="16" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="37"/>
+      <c r="B16" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>62</v>
@@ -1879,17 +1882,17 @@
         <v>90</v>
       </c>
       <c r="F16" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="37"/>
+      <c r="B17" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="15"/>
-    </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="28"/>
-      <c r="B17" s="35" t="s">
-        <v>120</v>
-      </c>
       <c r="C17" s="17" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>63</v>
@@ -1898,19 +1901,19 @@
         <v>60</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G17" s="15">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="28"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="37"/>
       <c r="B18" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>60</v>
@@ -1919,17 +1922,19 @@
         <v>60</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="15"/>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
-      <c r="B19" s="36" t="s">
-        <v>122</v>
+        <v>87</v>
+      </c>
+      <c r="G18" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="37"/>
+      <c r="B19" s="30" t="s">
+        <v>118</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>61</v>
@@ -1938,12 +1943,12 @@
         <v>120</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G19" s="15"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="28"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="37"/>
       <c r="B20" s="13" t="s">
         <v>75</v>
       </c>
@@ -1953,16 +1958,18 @@
         <v>45</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="15"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="28">
+        <v>87</v>
+      </c>
+      <c r="G20" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="37">
         <v>4</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="15"/>
@@ -1970,17 +1977,19 @@
         <v>45</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="15"/>
-    </row>
-    <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="28"/>
-      <c r="B22" s="37" t="s">
-        <v>124</v>
+        <v>87</v>
+      </c>
+      <c r="G21" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="37"/>
+      <c r="B22" s="31" t="s">
+        <v>120</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>64</v>
@@ -1989,14 +1998,14 @@
         <v>90</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G22" s="15"/>
     </row>
-    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="28"/>
-      <c r="B23" s="35" t="s">
-        <v>125</v>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="37"/>
+      <c r="B23" s="29" t="s">
+        <v>121</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>65</v>
@@ -2008,19 +2017,19 @@
         <v>60</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G23" s="15">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="28"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="37"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>60</v>
@@ -2029,17 +2038,19 @@
         <v>60</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="15"/>
-    </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="28"/>
-      <c r="B25" s="36" t="s">
-        <v>126</v>
+        <v>87</v>
+      </c>
+      <c r="G24" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="37"/>
+      <c r="B25" s="30" t="s">
+        <v>122</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>61</v>
@@ -2048,12 +2059,12 @@
         <v>120</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G25" s="15"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="28"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="37"/>
       <c r="B26" s="13" t="s">
         <v>75</v>
       </c>
@@ -2065,12 +2076,12 @@
       <c r="F26" s="25"/>
       <c r="G26" s="15"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="28">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="37">
         <v>5</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="15"/>
@@ -2080,13 +2091,13 @@
       <c r="F27" s="25"/>
       <c r="G27" s="15"/>
     </row>
-    <row r="28" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="28"/>
-      <c r="B28" s="37" t="s">
-        <v>127</v>
+    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="37"/>
+      <c r="B28" s="31" t="s">
+        <v>123</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>67</v>
@@ -2095,38 +2106,38 @@
         <v>90</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G28" s="15"/>
     </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="28"/>
-      <c r="B29" s="13" t="s">
-        <v>106</v>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="37"/>
+      <c r="B29" s="29" t="s">
+        <v>103</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E29" s="13">
         <v>120</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G29" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="28"/>
+    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="37"/>
       <c r="B30" s="13" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>69</v>
@@ -2135,12 +2146,12 @@
         <v>60</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G30" s="15"/>
     </row>
-    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="28"/>
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="37"/>
       <c r="B31" s="13" t="s">
         <v>70</v>
       </c>
@@ -2154,45 +2165,45 @@
         <v>60</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G31" s="15"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="28"/>
-      <c r="B32" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="40" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="37"/>
+      <c r="B32" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="34" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="13">
         <v>45</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G32" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
       <c r="F33" s="26"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G34">
         <f>+SUM(G2:G33)</f>
-        <v>18.5</v>
+        <v>33.5</v>
       </c>
     </row>
   </sheetData>
